--- a/artfynd/A 39638-2024 artfynd.xlsx
+++ b/artfynd/A 39638-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120114839</v>
       </c>
       <c r="B2" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 39638-2024 artfynd.xlsx
+++ b/artfynd/A 39638-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,107 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132692279</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93192</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vattensjöberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>526241</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6934310</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristin Lindström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristin Lindström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39638-2024 artfynd.xlsx
+++ b/artfynd/A 39638-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>132692279</v>
       </c>
       <c r="B3" t="n">
-        <v>93192</v>
+        <v>93196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39638-2024 artfynd.xlsx
+++ b/artfynd/A 39638-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>132692279</v>
       </c>
       <c r="B3" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39638-2024 artfynd.xlsx
+++ b/artfynd/A 39638-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441990</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132692279</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120114839</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,8 +1123,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441993</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>